--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:08:41+00:00</t>
+    <t>2023-09-20T08:13:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T08:13:12+00:00</t>
+    <t>2023-09-20T08:41:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T08:41:08+00:00</t>
+    <t>2023-09-20T09:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T09:03:25+00:00</t>
+    <t>2023-09-20T10:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T10:04:59+00:00</t>
+    <t>2023-09-20T11:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T11:27:18+00:00</t>
+    <t>2023-09-20T11:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-update-template/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T11:28:32+00:00</t>
+    <t>2023-09-20T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
